--- a/Anforderungsliste/AFL_LineXpress.xlsx
+++ b/Anforderungsliste/AFL_LineXpress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zhaw.sharepoint.com/sites/PM1Flaschenarbeit/Freigegebene Dokumente/General/PM2_Roboter_Projekt/Anforderungsliste/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\recjo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="409" documentId="8_{A61C2919-8077-4A04-8DAE-99AE28EB0645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6D70F2-6C8C-46FA-862C-3BA15D8EFE64}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE802DB9-1C51-44AF-B4E2-CAE2ED803B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
   <si>
     <t>Anforderungsliste für ein Paket-Roboters</t>
   </si>
@@ -115,9 +115,6 @@
     <t xml:space="preserve">Spurhaltung </t>
   </si>
   <si>
-    <t>Fahrzeug muss auf der Spurbleiben und an den Stopps halten</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wiederholbarkeit </t>
   </si>
   <si>
@@ -158,9 +155,6 @@
   </si>
   <si>
     <t>Fahrwerk</t>
-  </si>
-  <si>
-    <t>Genügend Traktion für Beschleunigung, Bremsen, sowie</t>
   </si>
   <si>
     <t>Fahrstabilität</t>
@@ -297,9 +291,6 @@
   </si>
   <si>
     <t>Abgabe Dokumentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Die Berichte müssen in SW 14 am Abend des 23.5. abgegeben werden.</t>
   </si>
   <si>
     <t>Abgabe Video</t>
@@ -347,6 +338,42 @@
   </si>
   <si>
     <t>Stabil bei Fehlmanöver</t>
+  </si>
+  <si>
+    <t>Fahrzeug muss auf der Spur bleiben und an den Stopps halten</t>
+  </si>
+  <si>
+    <t>Genügend Traktion für Beschleunigung, Bremsen.</t>
+  </si>
+  <si>
+    <t>Die Berichte müssen in SW 14 am Abend des 23.5. abgegeben werden.</t>
+  </si>
+  <si>
+    <t>Intelligente Routenstrategie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effizientiste Route </t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Strukturierte Softwarearchitektur</t>
+  </si>
+  <si>
+    <t>Fehler-Logging über LED-Codes</t>
+  </si>
+  <si>
+    <t>Parametrierbarkeit</t>
+  </si>
+  <si>
+    <t>PID-Werte / Schwellenwerte anpassbar ohne Code-Umbau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fehler klar erkennbar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übersichtlich / Kommentiert </t>
   </si>
 </sst>
 </file>
@@ -420,7 +447,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -697,17 +724,6 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -772,15 +788,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -929,7 +936,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -943,174 +950,164 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1131,8 +1128,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Besuchter Hyperlink" xfId="4" builtinId="9" hidden="1"/>
@@ -1449,63 +1468,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:I103"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="3.375" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" customWidth="1"/>
     <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="4" max="4" width="45.875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.375" style="23" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="45.8984375" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.3984375" style="23" customWidth="1"/>
+    <col min="6" max="6" width="14.09765625" customWidth="1"/>
     <col min="7" max="7" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.95" thickBot="1"/>
+    <row r="1" spans="2:6" ht="16.2" thickBot="1"/>
     <row r="2" spans="2:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B2" s="63"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="51" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="61" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="59" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="65"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
     </row>
     <row r="4" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1">
-      <c r="B4" s="65"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="55" t="s">
+      <c r="B4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="59" t="s">
+      <c r="E4" s="54"/>
+      <c r="F4" s="57" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1" thickBot="1">
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="57" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="60"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="58"/>
     </row>
     <row r="6" spans="2:6" ht="32.1" customHeight="1">
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="70"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="48"/>
     </row>
     <row r="7" spans="2:6" ht="51" customHeight="1" thickBot="1">
       <c r="B7" s="5" t="s">
@@ -1524,7 +1543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1">
+    <row r="8" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B8" s="11"/>
       <c r="C8" s="12">
         <v>1</v>
@@ -1533,16 +1552,16 @@
         <v>11</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="71" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:6" s="4" customFormat="1" ht="30.95">
+    <row r="9" spans="2:6" s="4" customFormat="1" ht="31.2">
       <c r="B9" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="21">
-        <v>1.1000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>14</v>
@@ -1550,14 +1569,14 @@
       <c r="E9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="48"/>
+      <c r="F9" s="72"/>
     </row>
     <row r="10" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
       <c r="B10" s="20" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="21">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>17</v>
@@ -1565,14 +1584,14 @@
       <c r="E10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="48"/>
+      <c r="F10" s="72"/>
     </row>
     <row r="11" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
       <c r="B11" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="21">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>19</v>
@@ -1580,731 +1599,819 @@
       <c r="E11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="48"/>
+      <c r="F11" s="72"/>
     </row>
     <row r="12" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
       <c r="B12" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="21">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="72"/>
+    </row>
+    <row r="13" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B13" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="21">
+        <v>1.05</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="48"/>
-    </row>
-    <row r="13" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B13" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="21">
-        <v>1.5</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="F13" s="72"/>
+    </row>
+    <row r="14" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B14" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="21">
+        <v>1.06</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="48"/>
-    </row>
-    <row r="14" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B14" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="21">
-        <v>1.6</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="F14" s="72"/>
+    </row>
+    <row r="15" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B15" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="21">
+        <v>1.07</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="48"/>
-    </row>
-    <row r="15" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B15" s="15"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="72"/>
+    </row>
+    <row r="16" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
+      <c r="B16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1.08</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="72"/>
+    </row>
+    <row r="17" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B17" s="29"/>
+      <c r="C17" s="43">
+        <v>2</v>
+      </c>
+      <c r="D17" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="48"/>
-    </row>
-    <row r="16" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1" thickBot="1">
-      <c r="B16" s="15"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="48"/>
-    </row>
-    <row r="17" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1" thickTop="1">
-      <c r="B17" s="29"/>
-      <c r="C17" s="27">
-        <v>2</v>
-      </c>
-      <c r="D17" s="30" t="s">
+      <c r="E17" s="31"/>
+      <c r="F17" s="72"/>
+    </row>
+    <row r="18" spans="2:8" s="4" customFormat="1">
+      <c r="B18" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="67">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D18" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="48"/>
-    </row>
-    <row r="18" spans="2:8" s="4" customFormat="1">
-      <c r="B18" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="33">
+      <c r="E18" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="72"/>
+    </row>
+    <row r="19" spans="2:8" s="4" customFormat="1">
+      <c r="B19" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="69">
+        <v>2.02</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="72"/>
+    </row>
+    <row r="20" spans="2:8" s="4" customFormat="1" ht="31.2">
+      <c r="B20" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="69">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="72"/>
+    </row>
+    <row r="21" spans="2:8" s="4" customFormat="1" ht="31.2">
+      <c r="B21" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="69">
+        <v>2.04</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="72"/>
+    </row>
+    <row r="22" spans="2:8" s="4" customFormat="1" ht="31.2">
+      <c r="B22" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="69">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="72"/>
+    </row>
+    <row r="23" spans="2:8" s="4" customFormat="1">
+      <c r="B23" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="69">
+        <v>2.06</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="72"/>
+    </row>
+    <row r="24" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B24" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="69">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="72"/>
+    </row>
+    <row r="25" spans="2:8" s="4" customFormat="1">
+      <c r="B25" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="69">
+        <v>2.08</v>
+      </c>
+      <c r="D25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="72"/>
+    </row>
+    <row r="26" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B26" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="69">
+        <v>2.09</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="72"/>
+      <c r="H26"/>
+    </row>
+    <row r="27" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B27" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="69">
         <v>2.1</v>
       </c>
-      <c r="D18" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="48"/>
-    </row>
-    <row r="19" spans="2:8" s="4" customFormat="1">
-      <c r="B19" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="48"/>
-    </row>
-    <row r="20" spans="2:8" s="4" customFormat="1" ht="30.95">
-      <c r="B20" s="15" t="s">
+      <c r="D27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="72"/>
+    </row>
+    <row r="28" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B28" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="69">
+        <v>2.11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="72"/>
+    </row>
+    <row r="29" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B29" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="69">
+        <v>2.12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="72"/>
+    </row>
+    <row r="30" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B30" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="69">
+        <v>2.13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="72"/>
+    </row>
+    <row r="31" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B31" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="69">
+        <v>2.14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="72"/>
+    </row>
+    <row r="32" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B32" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="48"/>
-    </row>
-    <row r="21" spans="2:8" s="4" customFormat="1" ht="30.95">
-      <c r="B21" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="48"/>
-    </row>
-    <row r="22" spans="2:8" s="4" customFormat="1" ht="30.95">
-      <c r="B22" s="15" t="s">
+      <c r="C32" s="69">
+        <v>2.15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="72"/>
+    </row>
+    <row r="33" spans="2:9" s="4" customFormat="1" ht="31.2">
+      <c r="B33" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="48"/>
-    </row>
-    <row r="23" spans="2:8" s="4" customFormat="1">
-      <c r="B23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="48"/>
-    </row>
-    <row r="24" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B24" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="48"/>
-    </row>
-    <row r="25" spans="2:8" s="4" customFormat="1">
-      <c r="B25" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="48"/>
-    </row>
-    <row r="26" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B26" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="48"/>
-      <c r="H26"/>
-    </row>
-    <row r="27" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B27" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="48"/>
-    </row>
-    <row r="28" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B28" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="48"/>
-    </row>
-    <row r="29" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B29" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="48"/>
-    </row>
-    <row r="30" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B30" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="48"/>
-    </row>
-    <row r="31" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B31" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" t="s">
+      <c r="C33" s="69">
+        <v>2.16</v>
+      </c>
+      <c r="D33" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="48"/>
-    </row>
-    <row r="32" spans="2:8" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B32" s="15" t="s">
+      <c r="E33" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="72"/>
+    </row>
+    <row r="34" spans="2:9" s="4" customFormat="1" ht="46.8">
+      <c r="B34" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="48"/>
-    </row>
-    <row r="33" spans="2:6" s="4" customFormat="1" ht="30.95">
-      <c r="B33" s="15" t="s">
+      <c r="C34" s="69">
+        <v>2.17</v>
+      </c>
+      <c r="D34" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="72"/>
+    </row>
+    <row r="35" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B35" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="48"/>
-    </row>
-    <row r="34" spans="2:6" s="4" customFormat="1" ht="46.5">
-      <c r="B34" s="15" t="s">
+      <c r="C35" s="69">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35" s="72"/>
+    </row>
+    <row r="36" spans="2:9" s="4" customFormat="1" ht="47.4" thickBot="1">
+      <c r="B36" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="48"/>
-    </row>
-    <row r="35" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B35" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" t="s">
+      <c r="C36" s="70">
+        <v>2.19</v>
+      </c>
+      <c r="D36" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F35" s="48"/>
-    </row>
-    <row r="36" spans="2:6" s="4" customFormat="1" ht="47.1" thickBot="1">
-      <c r="B36" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="48"/>
-    </row>
-    <row r="37" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1" thickTop="1">
+      <c r="F36" s="72"/>
+    </row>
+    <row r="37" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
       <c r="B37" s="29"/>
       <c r="C37" s="27">
         <v>3</v>
       </c>
       <c r="D37" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="28"/>
+      <c r="F37" s="72"/>
+    </row>
+    <row r="38" spans="2:9" s="4" customFormat="1" ht="31.35" customHeight="1">
+      <c r="B38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="33">
+        <v>3.01</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="48"/>
-    </row>
-    <row r="38" spans="2:6" s="4" customFormat="1" ht="31.35" customHeight="1">
-      <c r="B38" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="33">
-        <v>3.1</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="F38" s="72"/>
+    </row>
+    <row r="39" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B39" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="7">
+        <v>3.02</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="72"/>
+    </row>
+    <row r="40" spans="2:9" s="4" customFormat="1" ht="43.35" customHeight="1">
+      <c r="B40" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="7">
+        <v>3.03</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E40" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F38" s="49"/>
-    </row>
-    <row r="39" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B39" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="7">
-        <v>3.2</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F39" s="49"/>
-    </row>
-    <row r="40" spans="2:6" s="4" customFormat="1" ht="43.35" customHeight="1">
-      <c r="B40" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="7">
-        <v>3.3</v>
-      </c>
-      <c r="D40" s="4" t="s">
+      <c r="F40" s="72"/>
+    </row>
+    <row r="41" spans="2:9" s="4" customFormat="1" ht="64.349999999999994" customHeight="1">
+      <c r="B41" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="7">
+        <v>3.04</v>
+      </c>
+      <c r="D41" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E41" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F40" s="49"/>
-    </row>
-    <row r="41" spans="2:6" s="4" customFormat="1" ht="64.349999999999994" customHeight="1">
-      <c r="B41" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="7">
-        <v>3.4</v>
-      </c>
-      <c r="D41" s="37" t="s">
+      <c r="F41" s="72"/>
+    </row>
+    <row r="42" spans="2:9" s="4" customFormat="1" ht="60" customHeight="1">
+      <c r="B42" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="7">
+        <v>3.05</v>
+      </c>
+      <c r="D42" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E42" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F41" s="49"/>
-    </row>
-    <row r="42" spans="2:6" s="4" customFormat="1" ht="60" customHeight="1">
-      <c r="B42" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="D42" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F42" s="49"/>
-    </row>
-    <row r="43" spans="2:6" s="4" customFormat="1" ht="151.35" customHeight="1">
+      <c r="F42" s="72"/>
+    </row>
+    <row r="43" spans="2:9" s="4" customFormat="1" ht="151.35" customHeight="1">
       <c r="B43" s="36" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="7">
-        <v>3.6</v>
-      </c>
-      <c r="D43" s="34" t="s">
+        <v>3.06</v>
+      </c>
+      <c r="D43" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F43" s="72"/>
+    </row>
+    <row r="44" spans="2:9" s="4" customFormat="1" ht="53.4" customHeight="1">
+      <c r="B44" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="7">
+        <v>3.07</v>
+      </c>
+      <c r="D44" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E44" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F43" s="49"/>
-    </row>
-    <row r="44" spans="2:6" s="4" customFormat="1" ht="41.45" customHeight="1">
-      <c r="B44" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="D44" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F44" s="49"/>
-    </row>
-    <row r="45" spans="2:6" s="4" customFormat="1" ht="35.450000000000003" customHeight="1" thickBot="1">
+      <c r="F44" s="72"/>
+    </row>
+    <row r="45" spans="2:9" s="4" customFormat="1" ht="35.4" customHeight="1" thickBot="1">
       <c r="B45" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="38">
-        <v>3.8</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>73</v>
+      <c r="C45" s="7">
+        <v>3.08</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>71</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="F45" s="49"/>
-    </row>
-    <row r="46" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1" thickTop="1">
+        <v>72</v>
+      </c>
+      <c r="F45" s="72"/>
+    </row>
+    <row r="46" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
       <c r="B46" s="29"/>
       <c r="C46" s="27">
         <v>4</v>
       </c>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="28"/>
+      <c r="F46" s="72"/>
+    </row>
+    <row r="47" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B47" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="33">
+        <v>4.01</v>
+      </c>
+      <c r="D47" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="72"/>
+    </row>
+    <row r="48" spans="2:9" s="4" customFormat="1" ht="48" customHeight="1">
+      <c r="B48" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="7">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="72"/>
+      <c r="H48" s="3"/>
+      <c r="I48"/>
+    </row>
+    <row r="49" spans="2:9" s="4" customFormat="1" ht="33.6" customHeight="1" thickBot="1">
+      <c r="B49" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="7">
+        <v>4.03</v>
+      </c>
+      <c r="D49" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F49" s="72"/>
+    </row>
+    <row r="50" spans="2:9" s="4" customFormat="1" ht="16.8" customHeight="1" thickTop="1">
+      <c r="B50" s="29"/>
+      <c r="C50" s="27">
+        <v>5</v>
+      </c>
+      <c r="D50" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="28"/>
+      <c r="F50" s="72"/>
+    </row>
+    <row r="51" spans="2:9" s="4" customFormat="1">
+      <c r="B51" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="33">
+        <v>5.01</v>
+      </c>
+      <c r="D51" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E46" s="28"/>
-      <c r="F46" s="49"/>
-    </row>
-    <row r="47" spans="2:6" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B47" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="33">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="F51" s="72"/>
+      <c r="I51" s="8"/>
+    </row>
+    <row r="52" spans="2:9" s="4" customFormat="1" ht="31.2">
+      <c r="B52" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="E52" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F47" s="49"/>
-    </row>
-    <row r="48" spans="2:6" s="4" customFormat="1" ht="48" customHeight="1">
-      <c r="B48" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="7">
-        <v>4.2</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="F52" s="72"/>
+      <c r="I52" s="8"/>
+    </row>
+    <row r="53" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B53" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7">
+        <v>5.03</v>
+      </c>
+      <c r="D53" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E53" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="72"/>
+    </row>
+    <row r="54" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
+      <c r="B54" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="7">
+        <v>5.04</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F48" s="49"/>
-    </row>
-    <row r="49" spans="2:9" s="4" customFormat="1" ht="33.6" customHeight="1">
-      <c r="B49" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="7">
-        <v>4.3</v>
-      </c>
-      <c r="D49" s="37" t="s">
+      <c r="E54" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="F54" s="72"/>
+    </row>
+    <row r="55" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B55" s="29"/>
+      <c r="C55" s="32">
+        <v>6</v>
+      </c>
+      <c r="D55" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="F49" s="49"/>
-    </row>
-    <row r="50" spans="2:9" s="4" customFormat="1" ht="54" customHeight="1" thickBot="1">
-      <c r="B50" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="7">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D50" s="9" t="s">
+      <c r="E55" s="28"/>
+      <c r="F55" s="72"/>
+    </row>
+    <row r="56" spans="2:9" ht="15.9" customHeight="1">
+      <c r="B56" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="33">
+        <v>6.01</v>
+      </c>
+      <c r="D56" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E56" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F50" s="49"/>
-    </row>
-    <row r="51" spans="2:9" s="4" customFormat="1" ht="15.95" thickTop="1">
-      <c r="B51" s="29"/>
-      <c r="C51" s="32">
-        <v>5</v>
-      </c>
-      <c r="D51" s="30" t="s">
+      <c r="F56" s="72"/>
+    </row>
+    <row r="57" spans="2:9" ht="15.9" customHeight="1" thickBot="1">
+      <c r="B57" s="15"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="72"/>
+    </row>
+    <row r="58" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B58" s="29"/>
+      <c r="C58" s="27">
+        <v>7</v>
+      </c>
+      <c r="D58" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="E51" s="28"/>
-      <c r="F51" s="49"/>
-      <c r="I51" s="8"/>
-    </row>
-    <row r="52" spans="2:9" s="4" customFormat="1" ht="139.5">
-      <c r="B52" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="33">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D52" s="34" t="s">
+      <c r="E58" s="28"/>
+      <c r="F58" s="72"/>
+    </row>
+    <row r="59" spans="2:9" ht="15.9" customHeight="1">
+      <c r="B59" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="33">
+        <v>7.01</v>
+      </c>
+      <c r="D59" t="s">
         <v>85</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E59" s="24"/>
+      <c r="F59" s="72"/>
+    </row>
+    <row r="60" spans="2:9" ht="30" customHeight="1" thickBot="1">
+      <c r="B60" s="16"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="72"/>
+    </row>
+    <row r="61" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B61" s="29"/>
+      <c r="C61" s="43">
+        <v>8</v>
+      </c>
+      <c r="D61" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="F52" s="49"/>
-      <c r="I52" s="8"/>
-    </row>
-    <row r="53" spans="2:9" s="4" customFormat="1" ht="15.95" customHeight="1" thickBot="1">
-      <c r="B53" s="15"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="49"/>
-    </row>
-    <row r="54" spans="2:9" s="4" customFormat="1" ht="15.95" customHeight="1" thickTop="1">
-      <c r="B54" s="29"/>
-      <c r="C54" s="27">
-        <v>6</v>
-      </c>
-      <c r="D54" s="30" t="s">
+      <c r="E61" s="28"/>
+      <c r="F61" s="72"/>
+    </row>
+    <row r="62" spans="2:9" ht="15.9" customHeight="1">
+      <c r="B62" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="33">
+        <v>8.01</v>
+      </c>
+      <c r="D62" t="s">
         <v>87</v>
       </c>
-      <c r="E54" s="28"/>
-      <c r="F54" s="49"/>
-    </row>
-    <row r="55" spans="2:9" s="4" customFormat="1" ht="15.95" customHeight="1">
-      <c r="B55" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="33">
-        <v>6.1</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="E62" s="24"/>
+      <c r="F62" s="72"/>
+    </row>
+    <row r="63" spans="2:9" ht="15.9" customHeight="1">
+      <c r="B63" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="7">
+        <v>8.02</v>
+      </c>
+      <c r="D63" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="E55" s="24"/>
-      <c r="F55" s="49"/>
-    </row>
-    <row r="56" spans="2:9" ht="15.95" customHeight="1" thickBot="1">
-      <c r="B56" s="16"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="49"/>
-    </row>
-    <row r="57" spans="2:9" ht="15.95" customHeight="1" thickTop="1">
-      <c r="B57" s="29"/>
-      <c r="C57" s="44">
-        <v>7</v>
-      </c>
-      <c r="D57" s="30" t="s">
+      <c r="E63" s="25"/>
+      <c r="F63" s="72"/>
+    </row>
+    <row r="64" spans="2:9" ht="15.9" customHeight="1">
+      <c r="B64" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="7">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="D64" t="s">
         <v>89</v>
       </c>
-      <c r="E57" s="28"/>
-    </row>
-    <row r="58" spans="2:9" ht="15.95" customHeight="1">
-      <c r="B58" s="43" t="s">
+      <c r="E64" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="F64" s="72"/>
+    </row>
+    <row r="65" spans="2:6" ht="15.9" customHeight="1" thickBot="1">
+      <c r="B65" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="33">
-        <v>7.1</v>
-      </c>
-      <c r="D58" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="24"/>
-    </row>
-    <row r="59" spans="2:9" ht="15.95" customHeight="1">
-      <c r="B59" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" s="7">
-        <v>7.2</v>
-      </c>
-      <c r="D59" s="37" t="s">
+      <c r="C65" s="44">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="D65" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="E59" s="25"/>
-    </row>
-    <row r="60" spans="2:9" ht="30" customHeight="1">
-      <c r="B60" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="7">
-        <v>7.3</v>
-      </c>
-      <c r="D60" t="s">
-        <v>92</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="15.95" customHeight="1" thickBot="1">
-      <c r="B61" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="45">
-        <v>7.4</v>
-      </c>
-      <c r="D61" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="E61" s="26"/>
-    </row>
-    <row r="62" spans="2:9" ht="15.95" customHeight="1">
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-    </row>
-    <row r="63" spans="2:9" ht="15.95" customHeight="1">
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-    </row>
-    <row r="64" spans="2:9" ht="15.95" customHeight="1">
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-    </row>
-    <row r="66" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-    </row>
-    <row r="67" spans="2:3">
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-    </row>
-    <row r="68" spans="2:3">
+      <c r="E65" s="26"/>
+      <c r="F65" s="72"/>
+    </row>
+    <row r="66" spans="2:6" ht="15.9" customHeight="1"/>
+    <row r="68" spans="2:6">
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
     </row>
-    <row r="69" spans="2:3">
+    <row r="69" spans="2:6">
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
     </row>
-    <row r="70" spans="2:3">
+    <row r="70" spans="2:6">
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
     </row>
-    <row r="71" spans="2:3">
+    <row r="71" spans="2:6">
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
     </row>
-    <row r="72" spans="2:3">
+    <row r="72" spans="2:6">
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
     </row>
-    <row r="73" spans="2:3">
+    <row r="73" spans="2:6">
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
     </row>
-    <row r="74" spans="2:3">
+    <row r="74" spans="2:6">
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
     </row>
-    <row r="75" spans="2:3">
+    <row r="75" spans="2:6">
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
     </row>
-    <row r="76" spans="2:3">
+    <row r="76" spans="2:6">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
     </row>
-    <row r="77" spans="2:3">
+    <row r="77" spans="2:6">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
     </row>
-    <row r="78" spans="2:3">
+    <row r="78" spans="2:6">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
     </row>
-    <row r="79" spans="2:3">
+    <row r="79" spans="2:6">
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
     </row>
-    <row r="80" spans="2:3">
+    <row r="80" spans="2:6">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
     </row>
@@ -2402,7 +2509,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="F8:F56"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="D2:E3"/>
     <mergeCell ref="D4:E4"/>
@@ -2411,6 +2517,7 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="B4:C5"/>
+    <mergeCell ref="F8:F65"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2435,6 +2542,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101000549767899022646ADCD8372B4AFDD77" ma:contentTypeVersion="3" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="52dfa371bc222f35ed99d56e727d4f3c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8c0b0b4-a352-4ab5-8d9a-9b050095665e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f1c2f473d33a4499a8f2166cddfd851" ns2:_="">
     <xsd:import namespace="e8c0b0b4-a352-4ab5-8d9a-9b050095665e"/>
@@ -2572,20 +2685,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB680087-16DE-4BB1-9E43-BA0533F975EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB680087-16DE-4BB1-9E43-BA0533F975EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB33033-905C-4A15-BD49-8FA9F6ECA1E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA28E981-D323-4C4F-8BAF-D57797852A0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA28E981-D323-4C4F-8BAF-D57797852A0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB33033-905C-4A15-BD49-8FA9F6ECA1E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e8c0b0b4-a352-4ab5-8d9a-9b050095665e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Anforderungsliste/AFL_LineXpress.xlsx
+++ b/Anforderungsliste/AFL_LineXpress.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\recjo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paede\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE802DB9-1C51-44AF-B4E2-CAE2ED803B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7160B6D7-B4B0-4110-B45A-493B3103A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabelle1!$A$1:$G$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabelle1!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,6 +37,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -45,10 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
-  <si>
-    <t>Anforderungsliste für ein Paket-Roboters</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
   <si>
     <t>F = Forderung
 W = Wunsch</t>
@@ -57,10 +57,6 @@
     <t>Projekt:</t>
   </si>
   <si>
-    <t xml:space="preserve">Bearbeiter: 
-</t>
-  </si>
-  <si>
     <t>LineXpress</t>
   </si>
   <si>
@@ -85,9 +81,6 @@
     <t>Funktion</t>
   </si>
   <si>
-    <t>Team X</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -103,12 +96,6 @@
     <t>Zwischenlagerung der Pakete auf dem Roboter</t>
   </si>
   <si>
-    <t xml:space="preserve">evt. Für 4 Pakete gleichzeitig </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abflieferung der Pakete </t>
-  </si>
-  <si>
     <t>Richtige Positionierung bei der Abgabe</t>
   </si>
   <si>
@@ -220,9 +207,6 @@
     <t>Einfacher Zusammenbau</t>
   </si>
   <si>
-    <t>Bauteile müssen einzeln austauschbar sein, um defekte Teile einfach auszutauschen</t>
-  </si>
-  <si>
     <t>Wettkampfregeln</t>
   </si>
   <si>
@@ -233,9 +217,6 @@
   </si>
   <si>
     <t>Korrekte Zustellung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Das Paket am richtigen Haus liegt, es an der richtigen Position liegt </t>
   </si>
   <si>
     <t>Tunnel-Regeln</t>
@@ -281,13 +262,7 @@
     <t>Projektstart</t>
   </si>
   <si>
-    <t>Start der Übung U2 ist die SW 1</t>
-  </si>
-  <si>
     <t>Abgabe Videoskript</t>
-  </si>
-  <si>
-    <t>Domkument Video-Skript ist bis Mo 20.4 auf Moodle abgeben</t>
   </si>
   <si>
     <t>Abgabe Dokumentation</t>
@@ -334,9 +309,6 @@
     <t>Magnetische Störeinflüsse minimieren</t>
   </si>
   <si>
-    <t xml:space="preserve">Damit die Pakete nicht irgenwo steckenbleiben </t>
-  </si>
-  <si>
     <t>Stabil bei Fehlmanöver</t>
   </si>
   <si>
@@ -374,6 +346,55 @@
   </si>
   <si>
     <t xml:space="preserve">Übersichtlich / Kommentiert </t>
+  </si>
+  <si>
+    <t>Eco</t>
+  </si>
+  <si>
+    <t>Bauteile einzeln austauschbar, um defekte Teile einfach auszutauschen</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Das Paket muss bei der gleichen Farbe abgelegt werden, wie es aufgehoben wurde.</t>
+  </si>
+  <si>
+    <t>Dokument Video-Skript ist bis Mo 20.4 auf Moodle abgeben</t>
+  </si>
+  <si>
+    <t>Start des Projekts ist die SW 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ablieferung der Pakete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">evtl. Für 4 Pakete gleichzeitig </t>
+  </si>
+  <si>
+    <t>Anforderungsliste für Paketroboter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team 3
+</t>
+  </si>
+  <si>
+    <t>Betriebsdauer</t>
+  </si>
+  <si>
+    <t>genug Akku für mindestens 2 Durchläufe</t>
+  </si>
+  <si>
+    <t>Alle Kanten abgerundet</t>
+  </si>
+  <si>
+    <t>Kein Umkippen wenn der Arm im falschen Moment ausfährt</t>
+  </si>
+  <si>
+    <t>Teile brechen nicht ab bei Kollision mit Haus</t>
+  </si>
+  <si>
+    <t>Pakete fallen nicht ungewollt vom Magneten</t>
   </si>
 </sst>
 </file>
@@ -936,7 +957,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1056,9 +1077,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1068,7 +1086,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1110,9 +1145,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1128,29 +1160,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1467,7 +1493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I103"/>
+  <dimension ref="B1:I104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3.3984375" customWidth="1"/>
@@ -1480,67 +1506,69 @@
   <sheetData>
     <row r="1" spans="2:6" ht="16.2" thickBot="1"/>
     <row r="2" spans="2:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="49" t="s">
+      <c r="B2" s="73">
+        <v>46141</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="54"/>
+      <c r="F2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="59" t="s">
+    </row>
+    <row r="3" spans="2:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="64"/>
+    </row>
+    <row r="4" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1">
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="57" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-    </row>
-    <row r="4" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1">
-      <c r="B4" s="63"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="53" t="s">
+      <c r="E4" s="58"/>
+      <c r="F4" s="61" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1" thickBot="1">
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="57" t="s">
+      <c r="E5" s="60"/>
+      <c r="F5" s="62"/>
+    </row>
+    <row r="6" spans="2:6" ht="32.1" customHeight="1">
+      <c r="B6" s="50" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1" thickBot="1">
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="58"/>
-    </row>
-    <row r="6" spans="2:6" ht="32.1" customHeight="1">
-      <c r="B6" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="52"/>
     </row>
     <row r="7" spans="2:6" ht="51" customHeight="1" thickBot="1">
       <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="F7" s="10" t="s">
         <v>8</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
@@ -1549,824 +1577,843 @@
         <v>1</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="71" t="s">
-        <v>12</v>
+      <c r="F8" s="70" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="2:6" s="4" customFormat="1" ht="31.2">
       <c r="B9" s="20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="21">
         <v>1.01</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="72"/>
+        <v>12</v>
+      </c>
+      <c r="F9" s="71"/>
     </row>
     <row r="10" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
       <c r="B10" s="20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="21">
         <v>1.02</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="72"/>
+        <v>101</v>
+      </c>
+      <c r="F10" s="71"/>
     </row>
     <row r="11" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
       <c r="B11" s="20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="21">
         <v>1.03</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="72"/>
+        <v>15</v>
+      </c>
+      <c r="F11" s="71"/>
     </row>
     <row r="12" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
       <c r="B12" s="20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" s="21">
         <v>1.04</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="72"/>
+        <v>82</v>
+      </c>
+      <c r="F12" s="71"/>
     </row>
     <row r="13" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B13" s="20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13" s="21">
         <v>1.05</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="72"/>
+        <v>18</v>
+      </c>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B14" s="20" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" s="21">
         <v>1.06</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="72"/>
-    </row>
-    <row r="15" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="F14" s="71"/>
+    </row>
+    <row r="15" spans="2:6" s="4" customFormat="1" ht="31.2">
       <c r="B15" s="15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" s="21">
         <v>1.07</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="71"/>
+    </row>
+    <row r="16" spans="2:6" s="4" customFormat="1" ht="31.2">
+      <c r="B16" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="21">
+        <v>1.08</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="71"/>
+    </row>
+    <row r="17" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
+      <c r="B17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="71"/>
+    </row>
+    <row r="18" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B18" s="29"/>
+      <c r="C18" s="42">
+        <v>2</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="71"/>
+    </row>
+    <row r="19" spans="2:8" s="4" customFormat="1">
+      <c r="B19" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="44">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="71"/>
+    </row>
+    <row r="20" spans="2:8" s="4" customFormat="1">
+      <c r="B20" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="46">
+        <v>2.02</v>
+      </c>
+      <c r="D20" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E20" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="72"/>
-    </row>
-    <row r="16" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
-      <c r="B16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1.08</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="72"/>
-    </row>
-    <row r="17" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
-      <c r="B17" s="29"/>
-      <c r="C17" s="43">
-        <v>2</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="72"/>
-    </row>
-    <row r="18" spans="2:8" s="4" customFormat="1">
-      <c r="B18" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="67">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="D18" s="68" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="72"/>
-    </row>
-    <row r="19" spans="2:8" s="4" customFormat="1">
-      <c r="B19" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="69">
-        <v>2.02</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="72"/>
-    </row>
-    <row r="20" spans="2:8" s="4" customFormat="1" ht="31.2">
-      <c r="B20" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="69">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="72"/>
+      <c r="F20" s="71"/>
     </row>
     <row r="21" spans="2:8" s="4" customFormat="1" ht="31.2">
       <c r="B21" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="69">
-        <v>2.04</v>
+      <c r="C21" s="46">
+        <v>2.0299999999999998</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="72"/>
+        <v>29</v>
+      </c>
+      <c r="F21" s="71"/>
     </row>
     <row r="22" spans="2:8" s="4" customFormat="1" ht="31.2">
       <c r="B22" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="69">
-        <v>2.0499999999999998</v>
+        <v>10</v>
+      </c>
+      <c r="C22" s="46">
+        <v>2.04</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="72"/>
-    </row>
-    <row r="23" spans="2:8" s="4" customFormat="1">
+        <v>83</v>
+      </c>
+      <c r="F22" s="71"/>
+    </row>
+    <row r="23" spans="2:8" s="4" customFormat="1" ht="31.2">
       <c r="B23" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="69">
+      <c r="C23" s="46">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="71"/>
+    </row>
+    <row r="24" spans="2:8" s="4" customFormat="1">
+      <c r="B24" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="46">
         <v>2.06</v>
       </c>
-      <c r="D23" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="72"/>
-    </row>
-    <row r="24" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
-      <c r="B24" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="69">
+      <c r="D24" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="71"/>
+    </row>
+    <row r="25" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B25" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="46">
         <v>2.0699999999999998</v>
       </c>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="72"/>
-    </row>
-    <row r="25" spans="2:8" s="4" customFormat="1">
-      <c r="B25" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="69">
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="71"/>
+    </row>
+    <row r="26" spans="2:8" s="4" customFormat="1">
+      <c r="B26" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="46">
         <v>2.08</v>
       </c>
-      <c r="D25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="72"/>
-    </row>
-    <row r="26" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
-      <c r="B26" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="69">
-        <v>2.09</v>
-      </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="72"/>
-      <c r="H26"/>
+        <v>37</v>
+      </c>
+      <c r="F26" s="71"/>
     </row>
     <row r="27" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B27" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="69">
-        <v>2.1</v>
+        <v>10</v>
+      </c>
+      <c r="C27" s="46">
+        <v>2.09</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="72"/>
+        <v>37</v>
+      </c>
+      <c r="F27" s="71"/>
+      <c r="H27"/>
     </row>
     <row r="28" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B28" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="69">
-        <v>2.11</v>
+        <v>10</v>
+      </c>
+      <c r="C28" s="46">
+        <v>2.1</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="72"/>
+        <v>34</v>
+      </c>
+      <c r="F28" s="71"/>
     </row>
     <row r="29" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B29" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="69">
-        <v>2.12</v>
+        <v>10</v>
+      </c>
+      <c r="C29" s="46">
+        <v>2.11</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="72"/>
+        <v>34</v>
+      </c>
+      <c r="F29" s="71"/>
     </row>
     <row r="30" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B30" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="69">
-        <v>2.13</v>
+        <v>10</v>
+      </c>
+      <c r="C30" s="46">
+        <v>2.12</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F30" s="72"/>
+        <v>34</v>
+      </c>
+      <c r="F30" s="71"/>
     </row>
     <row r="31" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B31" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="69">
-        <v>2.14</v>
+        <v>10</v>
+      </c>
+      <c r="C31" s="46">
+        <v>2.13</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F31" s="72"/>
+        <v>34</v>
+      </c>
+      <c r="F31" s="71"/>
     </row>
     <row r="32" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B32" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="69">
+        <v>10</v>
+      </c>
+      <c r="C32" s="46">
+        <v>2.14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="71"/>
+    </row>
+    <row r="33" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B33" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="46">
         <v>2.15</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="71"/>
+    </row>
+    <row r="34" spans="2:6" s="4" customFormat="1" ht="31.2">
+      <c r="B34" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="46">
+        <v>2.16</v>
+      </c>
+      <c r="D34" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="71"/>
+    </row>
+    <row r="35" spans="2:6" s="4" customFormat="1" ht="46.8">
+      <c r="B35" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="46">
+        <v>2.17</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="71"/>
+    </row>
+    <row r="36" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B36" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="46">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="D36" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="72"/>
-    </row>
-    <row r="33" spans="2:9" s="4" customFormat="1" ht="31.2">
-      <c r="B33" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="69">
-        <v>2.16</v>
-      </c>
-      <c r="D33" s="34" t="s">
+      <c r="E36" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="F36" s="71"/>
+    </row>
+    <row r="37" spans="2:6" s="4" customFormat="1" ht="31.8" thickBot="1">
+      <c r="B37" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="47">
+        <v>2.19</v>
+      </c>
+      <c r="D37" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="F33" s="72"/>
-    </row>
-    <row r="34" spans="2:9" s="4" customFormat="1" ht="46.8">
-      <c r="B34" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="69">
-        <v>2.17</v>
-      </c>
-      <c r="D34" s="34" t="s">
+      <c r="E37" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="71"/>
+    </row>
+    <row r="38" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B38" s="29"/>
+      <c r="C38" s="27">
+        <v>3</v>
+      </c>
+      <c r="D38" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E38" s="28"/>
+      <c r="F38" s="71"/>
+    </row>
+    <row r="39" spans="2:6" s="4" customFormat="1" ht="31.35" customHeight="1">
+      <c r="B39" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="33">
+        <v>3.01</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F34" s="72"/>
-    </row>
-    <row r="35" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
-      <c r="B35" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="69">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E39" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="F39" s="71"/>
+    </row>
+    <row r="40" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B40" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>3.02</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="71"/>
+    </row>
+    <row r="41" spans="2:6" s="4" customFormat="1" ht="46.8">
+      <c r="B41" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>3.03</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="72"/>
-    </row>
-    <row r="36" spans="2:9" s="4" customFormat="1" ht="47.4" thickBot="1">
-      <c r="B36" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="70">
-        <v>2.19</v>
-      </c>
-      <c r="D36" s="34" t="s">
+      <c r="E41" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F41" s="71"/>
+    </row>
+    <row r="42" spans="2:6" s="4" customFormat="1" ht="64.349999999999994" customHeight="1">
+      <c r="B42" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>3.04</v>
+      </c>
+      <c r="D42" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E42" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F36" s="72"/>
-    </row>
-    <row r="37" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
-      <c r="B37" s="29"/>
-      <c r="C37" s="27">
-        <v>3</v>
-      </c>
-      <c r="D37" s="30" t="s">
+      <c r="F42" s="71"/>
+    </row>
+    <row r="43" spans="2:6" s="4" customFormat="1" ht="60" customHeight="1">
+      <c r="B43" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>3.05</v>
+      </c>
+      <c r="D43" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="72"/>
-    </row>
-    <row r="38" spans="2:9" s="4" customFormat="1" ht="31.35" customHeight="1">
-      <c r="B38" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="33">
-        <v>3.01</v>
-      </c>
-      <c r="D38" s="4" t="s">
+      <c r="E43" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="72"/>
-    </row>
-    <row r="39" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
-      <c r="B39" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="7">
-        <v>3.02</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="72"/>
-    </row>
-    <row r="40" spans="2:9" s="4" customFormat="1" ht="43.35" customHeight="1">
-      <c r="B40" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="7">
-        <v>3.03</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F40" s="72"/>
-    </row>
-    <row r="41" spans="2:9" s="4" customFormat="1" ht="64.349999999999994" customHeight="1">
-      <c r="B41" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="7">
-        <v>3.04</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="72"/>
-    </row>
-    <row r="42" spans="2:9" s="4" customFormat="1" ht="60" customHeight="1">
-      <c r="B42" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="7">
-        <v>3.05</v>
-      </c>
-      <c r="D42" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F42" s="72"/>
-    </row>
-    <row r="43" spans="2:9" s="4" customFormat="1" ht="151.35" customHeight="1">
-      <c r="B43" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="7">
-        <v>3.06</v>
-      </c>
-      <c r="D43" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F43" s="72"/>
-    </row>
-    <row r="44" spans="2:9" s="4" customFormat="1" ht="53.4" customHeight="1">
+      <c r="F43" s="71"/>
+    </row>
+    <row r="44" spans="2:6" s="4" customFormat="1" ht="151.35" customHeight="1">
       <c r="B44" s="36" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="7">
+        <v>3.06</v>
+      </c>
+      <c r="D44" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" s="71"/>
+    </row>
+    <row r="45" spans="2:6" s="4" customFormat="1" ht="53.4" customHeight="1">
+      <c r="B45" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
         <v>3.07</v>
       </c>
-      <c r="D44" s="34" t="s">
+      <c r="D45" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F45" s="71"/>
+    </row>
+    <row r="46" spans="2:6" s="4" customFormat="1" ht="35.4" customHeight="1" thickBot="1">
+      <c r="B46" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="7">
+        <v>3.08</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F46" s="71"/>
+    </row>
+    <row r="47" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B47" s="29"/>
+      <c r="C47" s="27">
+        <v>4</v>
+      </c>
+      <c r="D47" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" s="28"/>
+      <c r="F47" s="71"/>
+    </row>
+    <row r="48" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
+      <c r="B48" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="33">
+        <v>4.01</v>
+      </c>
+      <c r="D48" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" s="71"/>
+    </row>
+    <row r="49" spans="2:9" s="4" customFormat="1" ht="48" customHeight="1">
+      <c r="B49" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="7">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" s="71"/>
+      <c r="H49" s="3"/>
+      <c r="I49"/>
+    </row>
+    <row r="50" spans="2:9" s="4" customFormat="1" ht="33.6" customHeight="1" thickBot="1">
+      <c r="B50" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="7">
+        <v>4.03</v>
+      </c>
+      <c r="D50" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" s="71"/>
+    </row>
+    <row r="51" spans="2:9" s="4" customFormat="1" ht="16.8" customHeight="1" thickTop="1">
+      <c r="B51" s="29"/>
+      <c r="C51" s="27">
+        <v>5</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="28"/>
+      <c r="F51" s="71"/>
+    </row>
+    <row r="52" spans="2:9" s="4" customFormat="1">
+      <c r="B52" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="33">
+        <v>5.01</v>
+      </c>
+      <c r="D52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="F52" s="71"/>
+      <c r="I52" s="8"/>
+    </row>
+    <row r="53" spans="2:9" s="4" customFormat="1" ht="31.2">
+      <c r="B53" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="7">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F53" s="71"/>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" spans="2:9" s="4" customFormat="1" ht="31.2">
+      <c r="B54" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="7">
+        <v>5.03</v>
+      </c>
+      <c r="D54" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E54" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F54" s="71"/>
+    </row>
+    <row r="55" spans="2:9" s="4" customFormat="1" ht="47.4" thickBot="1">
+      <c r="B55" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="7">
+        <v>5.04</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F44" s="72"/>
-    </row>
-    <row r="45" spans="2:9" s="4" customFormat="1" ht="35.4" customHeight="1" thickBot="1">
-      <c r="B45" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="7">
-        <v>3.08</v>
-      </c>
-      <c r="D45" s="39" t="s">
+      <c r="E55" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E45" s="35" t="s">
+      <c r="F55" s="71"/>
+    </row>
+    <row r="56" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B56" s="29"/>
+      <c r="C56" s="32">
+        <v>6</v>
+      </c>
+      <c r="D56" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="F45" s="72"/>
-    </row>
-    <row r="46" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
-      <c r="B46" s="29"/>
-      <c r="C46" s="27">
-        <v>4</v>
-      </c>
-      <c r="D46" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="E46" s="28"/>
-      <c r="F46" s="72"/>
-    </row>
-    <row r="47" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
-      <c r="B47" s="14" t="s">
+      <c r="E56" s="28"/>
+      <c r="F56" s="71"/>
+    </row>
+    <row r="57" spans="2:9" ht="140.4">
+      <c r="B57" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="33">
+        <v>6.01</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="71"/>
+    </row>
+    <row r="58" spans="2:9" ht="15.9" customHeight="1" thickBot="1">
+      <c r="B58" s="15"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="71"/>
+    </row>
+    <row r="59" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B59" s="29"/>
+      <c r="C59" s="27">
+        <v>7</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="28"/>
+      <c r="F59" s="71"/>
+    </row>
+    <row r="60" spans="2:9" ht="15.9" customHeight="1">
+      <c r="B60" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="33">
+        <v>7.01</v>
+      </c>
+      <c r="D60" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="24"/>
+      <c r="F60" s="71"/>
+    </row>
+    <row r="61" spans="2:9" ht="30" customHeight="1" thickBot="1">
+      <c r="B61" s="16"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="71"/>
+    </row>
+    <row r="62" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
+      <c r="B62" s="29"/>
+      <c r="C62" s="42">
+        <v>8</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" s="28"/>
+      <c r="F62" s="71"/>
+    </row>
+    <row r="63" spans="2:9" ht="31.2">
+      <c r="B63" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="33">
-        <v>4.01</v>
-      </c>
-      <c r="D47" s="73" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="F47" s="72"/>
-    </row>
-    <row r="48" spans="2:9" s="4" customFormat="1" ht="48" customHeight="1">
-      <c r="B48" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="7">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F48" s="72"/>
-      <c r="H48" s="3"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="2:9" s="4" customFormat="1" ht="33.6" customHeight="1" thickBot="1">
-      <c r="B49" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="7">
-        <v>4.03</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="F49" s="72"/>
-    </row>
-    <row r="50" spans="2:9" s="4" customFormat="1" ht="16.8" customHeight="1" thickTop="1">
-      <c r="B50" s="29"/>
-      <c r="C50" s="27">
-        <v>5</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="28"/>
-      <c r="F50" s="72"/>
-    </row>
-    <row r="51" spans="2:9" s="4" customFormat="1">
-      <c r="B51" s="14" t="s">
+      <c r="C63" s="33">
+        <v>8.01</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F63" s="71"/>
+    </row>
+    <row r="64" spans="2:9">
+      <c r="B64" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="33">
-        <v>5.01</v>
-      </c>
-      <c r="D51" t="s">
-        <v>74</v>
-      </c>
-      <c r="E51" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="72"/>
-      <c r="I51" s="8"/>
-    </row>
-    <row r="52" spans="2:9" s="4" customFormat="1" ht="31.2">
-      <c r="B52" s="36" t="s">
+      <c r="C64" s="7">
+        <v>8.02</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="F64" s="71"/>
+    </row>
+    <row r="65" spans="2:6" ht="31.2">
+      <c r="B65" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C52" s="7">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F52" s="72"/>
-      <c r="I52" s="8"/>
-    </row>
-    <row r="53" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1">
-      <c r="B53" s="36" t="s">
+      <c r="C65" s="7">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" s="72" t="s">
+        <v>109</v>
+      </c>
+      <c r="F65" s="71"/>
+    </row>
+    <row r="66" spans="2:6" ht="31.8" thickBot="1">
+      <c r="B66" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="7">
-        <v>5.03</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F53" s="72"/>
-    </row>
-    <row r="54" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
-      <c r="B54" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="7">
-        <v>5.04</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F54" s="72"/>
-    </row>
-    <row r="55" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
-      <c r="B55" s="29"/>
-      <c r="C55" s="32">
-        <v>6</v>
-      </c>
-      <c r="D55" s="30" t="s">
+      <c r="C66" s="43">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="D66" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="72"/>
-    </row>
-    <row r="56" spans="2:9" ht="15.9" customHeight="1">
-      <c r="B56" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="33">
-        <v>6.01</v>
-      </c>
-      <c r="D56" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="E56" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="F56" s="72"/>
-    </row>
-    <row r="57" spans="2:9" ht="15.9" customHeight="1" thickBot="1">
-      <c r="B57" s="15"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="72"/>
-    </row>
-    <row r="58" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
-      <c r="B58" s="29"/>
-      <c r="C58" s="27">
-        <v>7</v>
-      </c>
-      <c r="D58" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="28"/>
-      <c r="F58" s="72"/>
-    </row>
-    <row r="59" spans="2:9" ht="15.9" customHeight="1">
-      <c r="B59" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="33">
-        <v>7.01</v>
-      </c>
-      <c r="D59" t="s">
-        <v>85</v>
-      </c>
-      <c r="E59" s="24"/>
-      <c r="F59" s="72"/>
-    </row>
-    <row r="60" spans="2:9" ht="30" customHeight="1" thickBot="1">
-      <c r="B60" s="16"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="72"/>
-    </row>
-    <row r="61" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
-      <c r="B61" s="29"/>
-      <c r="C61" s="43">
-        <v>8</v>
-      </c>
-      <c r="D61" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="72"/>
-    </row>
-    <row r="62" spans="2:9" ht="15.9" customHeight="1">
-      <c r="B62" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="33">
-        <v>8.01</v>
-      </c>
-      <c r="D62" t="s">
-        <v>87</v>
-      </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="72"/>
-    </row>
-    <row r="63" spans="2:9" ht="15.9" customHeight="1">
-      <c r="B63" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" s="7">
-        <v>8.02</v>
-      </c>
-      <c r="D63" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E63" s="25"/>
-      <c r="F63" s="72"/>
-    </row>
-    <row r="64" spans="2:9" ht="15.9" customHeight="1">
-      <c r="B64" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" s="7">
-        <v>8.0299999999999994</v>
-      </c>
-      <c r="D64" t="s">
-        <v>89</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F64" s="72"/>
-    </row>
-    <row r="65" spans="2:6" ht="15.9" customHeight="1" thickBot="1">
-      <c r="B65" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" s="44">
-        <v>8.0399999999999991</v>
-      </c>
-      <c r="D65" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="E65" s="26"/>
-      <c r="F65" s="72"/>
-    </row>
-    <row r="66" spans="2:6" ht="15.9" customHeight="1"/>
-    <row r="68" spans="2:6">
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-    </row>
+      <c r="E66" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F66" s="71"/>
+    </row>
+    <row r="67" spans="2:6" ht="15.9" customHeight="1"/>
     <row r="69" spans="2:6">
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2507,8 +2554,13 @@
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
     </row>
+    <row r="104" spans="2:3">
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="F8:F66"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="D2:E3"/>
     <mergeCell ref="D4:E4"/>
@@ -2517,14 +2569,13 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="B4:C5"/>
-    <mergeCell ref="F8:F65"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="77" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="36" max="6" man="1"/>
-    <brk id="56" max="16383" man="1"/>
+    <brk id="37" max="6" man="1"/>
+    <brk id="57" max="16383" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="7" max="1048575" man="1"/>
@@ -2542,12 +2593,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101000549767899022646ADCD8372B4AFDD77" ma:contentTypeVersion="3" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="52dfa371bc222f35ed99d56e727d4f3c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8c0b0b4-a352-4ab5-8d9a-9b050095665e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f1c2f473d33a4499a8f2166cddfd851" ns2:_="">
     <xsd:import namespace="e8c0b0b4-a352-4ab5-8d9a-9b050095665e"/>
@@ -2685,6 +2730,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB680087-16DE-4BB1-9E43-BA0533F975EB}">
   <ds:schemaRefs>
@@ -2694,15 +2745,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA28E981-D323-4C4F-8BAF-D57797852A0D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB33033-905C-4A15-BD49-8FA9F6ECA1E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2718,4 +2760,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA28E981-D323-4C4F-8BAF-D57797852A0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Anforderungsliste/AFL_LineXpress.xlsx
+++ b/Anforderungsliste/AFL_LineXpress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paede\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timok\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7160B6D7-B4B0-4110-B45A-493B3103A75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86240BB-A8F2-4E6F-B3DA-95079777D57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -57,9 +54,6 @@
     <t>Projekt:</t>
   </si>
   <si>
-    <t>LineXpress</t>
-  </si>
-  <si>
     <t>Anforderungen</t>
   </si>
   <si>
@@ -395,6 +389,9 @@
   </si>
   <si>
     <t>Pakete fallen nicht ungewollt vom Magneten</t>
+  </si>
+  <si>
+    <t>MoonCarrier</t>
   </si>
 </sst>
 </file>
@@ -468,7 +465,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -946,6 +943,17 @@
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -957,7 +965,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1098,11 +1106,23 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1133,21 +1153,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1160,23 +1165,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1494,81 +1505,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:I104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.58203125" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="3.3984375" customWidth="1"/>
+    <col min="1" max="1" width="3.4140625" customWidth="1"/>
     <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="4" max="4" width="45.8984375" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.3984375" style="23" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" customWidth="1"/>
+    <col min="4" max="4" width="45.9140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.4140625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="14.08203125" customWidth="1"/>
     <col min="7" max="7" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="16.2" thickBot="1"/>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B2" s="73">
-        <v>46141</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="53" t="s">
+    <row r="1" spans="2:6" ht="16" thickBot="1"/>
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="20.149999999999999" customHeight="1">
+      <c r="B2" s="69">
+        <v>46155</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="58"/>
+      <c r="F2" s="75" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" s="1" customFormat="1" ht="20.149999999999999" customHeight="1">
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="76"/>
+    </row>
+    <row r="4" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1">
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="62"/>
+      <c r="F4" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="63" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B3" s="66"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="64"/>
-    </row>
-    <row r="4" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1">
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="61" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="5" spans="2:6" s="1" customFormat="1" ht="27" customHeight="1" thickBot="1">
-      <c r="B5" s="68"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="59" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="64"/>
+      <c r="F5" s="74"/>
+    </row>
+    <row r="6" spans="2:6" ht="32.15" customHeight="1">
+      <c r="B6" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="60"/>
-      <c r="F5" s="62"/>
-    </row>
-    <row r="6" spans="2:6" ht="32.1" customHeight="1">
-      <c r="B6" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="52"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="56"/>
     </row>
     <row r="7" spans="2:6" ht="51" customHeight="1" thickBot="1">
       <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
@@ -1577,147 +1588,147 @@
         <v>1</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="13"/>
-      <c r="F8" s="70" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" s="4" customFormat="1" ht="31.2">
+      <c r="F8" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" s="4" customFormat="1" ht="31">
       <c r="B9" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="21">
         <v>1.01</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="53"/>
+    </row>
+    <row r="10" spans="2:6" s="4" customFormat="1" ht="32.15" customHeight="1">
+      <c r="B10" s="20" t="s">
         <v>12</v>
-      </c>
-      <c r="F9" s="71"/>
-    </row>
-    <row r="10" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
-      <c r="B10" s="20" t="s">
-        <v>13</v>
       </c>
       <c r="C10" s="21">
         <v>1.02</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="71"/>
-    </row>
-    <row r="11" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
+        <v>100</v>
+      </c>
+      <c r="F10" s="53"/>
+    </row>
+    <row r="11" spans="2:6" s="4" customFormat="1" ht="32.15" customHeight="1">
       <c r="B11" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="21">
         <v>1.03</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="71"/>
-    </row>
-    <row r="12" spans="2:6" s="4" customFormat="1" ht="32.1" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="F11" s="53"/>
+    </row>
+    <row r="12" spans="2:6" s="4" customFormat="1" ht="32.15" customHeight="1">
       <c r="B12" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="21">
         <v>1.04</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="71"/>
+        <v>81</v>
+      </c>
+      <c r="F12" s="53"/>
     </row>
     <row r="13" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B13" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="21">
         <v>1.05</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="71"/>
+      <c r="F13" s="53"/>
     </row>
     <row r="14" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B14" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="21">
         <v>1.06</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="71"/>
-    </row>
-    <row r="15" spans="2:6" s="4" customFormat="1" ht="31.2">
+      <c r="F14" s="53"/>
+    </row>
+    <row r="15" spans="2:6" s="4" customFormat="1" ht="31">
       <c r="B15" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="21">
         <v>1.07</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="71"/>
-    </row>
-    <row r="16" spans="2:6" s="4" customFormat="1" ht="31.2">
+      <c r="F15" s="53"/>
+    </row>
+    <row r="16" spans="2:6" s="4" customFormat="1" ht="31">
       <c r="B16" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" s="21">
         <v>1.08</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F16" s="71"/>
+      <c r="F16" s="53"/>
     </row>
     <row r="17" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1" thickBot="1">
       <c r="B17" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="7">
         <v>1.0900000000000001</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="71"/>
+      <c r="F17" s="53"/>
     </row>
     <row r="18" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
       <c r="B18" s="29"/>
@@ -1725,296 +1736,296 @@
         <v>2</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" s="31"/>
-      <c r="F18" s="71"/>
+      <c r="F18" s="53"/>
     </row>
     <row r="19" spans="2:8" s="4" customFormat="1">
       <c r="B19" s="41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="44">
         <v>2.0099999999999998</v>
       </c>
       <c r="D19" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="71"/>
+      <c r="F19" s="53"/>
     </row>
     <row r="20" spans="2:8" s="4" customFormat="1">
       <c r="B20" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" s="46">
         <v>2.02</v>
       </c>
       <c r="D20" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="71"/>
-    </row>
-    <row r="21" spans="2:8" s="4" customFormat="1" ht="31.2">
+      <c r="F20" s="53"/>
+    </row>
+    <row r="21" spans="2:8" s="4" customFormat="1" ht="31">
       <c r="B21" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="46">
         <v>2.0299999999999998</v>
       </c>
       <c r="D21" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="71"/>
-    </row>
-    <row r="22" spans="2:8" s="4" customFormat="1" ht="31.2">
+      <c r="F21" s="53"/>
+    </row>
+    <row r="22" spans="2:8" s="4" customFormat="1" ht="31">
       <c r="B22" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" s="46">
         <v>2.04</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="71"/>
-    </row>
-    <row r="23" spans="2:8" s="4" customFormat="1" ht="31.2">
+        <v>82</v>
+      </c>
+      <c r="F22" s="53"/>
+    </row>
+    <row r="23" spans="2:8" s="4" customFormat="1" ht="31">
       <c r="B23" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" s="46">
         <v>2.0499999999999998</v>
       </c>
       <c r="D23" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="71"/>
+      <c r="F23" s="53"/>
     </row>
     <row r="24" spans="2:8" s="4" customFormat="1">
       <c r="B24" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="46">
         <v>2.06</v>
       </c>
       <c r="D24" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="71"/>
+      <c r="F24" s="53"/>
     </row>
     <row r="25" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B25" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" s="46">
         <v>2.0699999999999998</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="71"/>
+        <v>33</v>
+      </c>
+      <c r="F25" s="53"/>
     </row>
     <row r="26" spans="2:8" s="4" customFormat="1">
       <c r="B26" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="46">
         <v>2.08</v>
       </c>
       <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="71"/>
+      <c r="F26" s="53"/>
     </row>
     <row r="27" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B27" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" s="46">
         <v>2.09</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="71"/>
+        <v>36</v>
+      </c>
+      <c r="F27" s="53"/>
       <c r="H27"/>
     </row>
     <row r="28" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B28" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="46">
         <v>2.1</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="71"/>
+        <v>33</v>
+      </c>
+      <c r="F28" s="53"/>
     </row>
     <row r="29" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B29" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="46">
         <v>2.11</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="71"/>
+        <v>33</v>
+      </c>
+      <c r="F29" s="53"/>
     </row>
     <row r="30" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B30" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="46">
         <v>2.12</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="71"/>
+        <v>33</v>
+      </c>
+      <c r="F30" s="53"/>
     </row>
     <row r="31" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B31" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="46">
         <v>2.13</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="71"/>
+        <v>33</v>
+      </c>
+      <c r="F31" s="53"/>
     </row>
     <row r="32" spans="2:8" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B32" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="46">
         <v>2.14</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="71"/>
+        <v>33</v>
+      </c>
+      <c r="F32" s="53"/>
     </row>
     <row r="33" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B33" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" s="46">
         <v>2.15</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="71"/>
-    </row>
-    <row r="34" spans="2:6" s="4" customFormat="1" ht="31.2">
+        <v>93</v>
+      </c>
+      <c r="F33" s="53"/>
+    </row>
+    <row r="34" spans="2:6" s="4" customFormat="1" ht="31">
       <c r="B34" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="46">
         <v>2.16</v>
       </c>
       <c r="D34" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F34" s="71"/>
-    </row>
-    <row r="35" spans="2:6" s="4" customFormat="1" ht="46.8">
+      <c r="F34" s="53"/>
+    </row>
+    <row r="35" spans="2:6" s="4" customFormat="1" ht="46.5">
       <c r="B35" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" s="46">
         <v>2.17</v>
       </c>
       <c r="D35" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" s="71"/>
+      <c r="F35" s="53"/>
     </row>
     <row r="36" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B36" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" s="46">
         <v>2.1800000000000002</v>
       </c>
       <c r="D36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F36" s="71"/>
-    </row>
-    <row r="37" spans="2:6" s="4" customFormat="1" ht="31.8" thickBot="1">
+      <c r="F36" s="53"/>
+    </row>
+    <row r="37" spans="2:6" s="4" customFormat="1" ht="31.5" thickBot="1">
       <c r="B37" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" s="47">
         <v>2.19</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="71"/>
+        <v>94</v>
+      </c>
+      <c r="F37" s="53"/>
     </row>
     <row r="38" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
       <c r="B38" s="29"/>
@@ -2022,130 +2033,130 @@
         <v>3</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E38" s="28"/>
-      <c r="F38" s="71"/>
-    </row>
-    <row r="39" spans="2:6" s="4" customFormat="1" ht="31.35" customHeight="1">
+      <c r="F38" s="53"/>
+    </row>
+    <row r="39" spans="2:6" s="4" customFormat="1" ht="31.4" customHeight="1">
       <c r="B39" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39" s="33">
         <v>3.01</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39" s="71"/>
+      <c r="F39" s="53"/>
     </row>
     <row r="40" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B40" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C40" s="7">
         <v>3.02</v>
       </c>
       <c r="D40" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E40" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="71"/>
-    </row>
-    <row r="41" spans="2:6" s="4" customFormat="1" ht="46.8">
+      <c r="F40" s="53"/>
+    </row>
+    <row r="41" spans="2:6" s="4" customFormat="1" ht="46.5">
       <c r="B41" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41" s="7">
         <v>3.03</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F41" s="71"/>
-    </row>
-    <row r="42" spans="2:6" s="4" customFormat="1" ht="64.349999999999994" customHeight="1">
+        <v>96</v>
+      </c>
+      <c r="F41" s="53"/>
+    </row>
+    <row r="42" spans="2:6" s="4" customFormat="1" ht="64.400000000000006" customHeight="1">
       <c r="B42" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42" s="7">
         <v>3.04</v>
       </c>
       <c r="D42" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" s="71"/>
+      <c r="F42" s="53"/>
     </row>
     <row r="43" spans="2:6" s="4" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" s="7">
         <v>3.05</v>
       </c>
       <c r="D43" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E43" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F43" s="71"/>
-    </row>
-    <row r="44" spans="2:6" s="4" customFormat="1" ht="151.35" customHeight="1">
+      <c r="F43" s="53"/>
+    </row>
+    <row r="44" spans="2:6" s="4" customFormat="1" ht="151.4" customHeight="1">
       <c r="B44" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" s="7">
         <v>3.06</v>
       </c>
-      <c r="D44" s="49" t="s">
+      <c r="D44" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F44" s="71"/>
+      <c r="F44" s="53"/>
     </row>
     <row r="45" spans="2:6" s="4" customFormat="1" ht="53.4" customHeight="1">
       <c r="B45" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" s="7">
         <v>3.07</v>
       </c>
       <c r="D45" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F45" s="71"/>
+      <c r="F45" s="53"/>
     </row>
     <row r="46" spans="2:6" s="4" customFormat="1" ht="35.4" customHeight="1" thickBot="1">
       <c r="B46" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" s="7">
         <v>3.08</v>
       </c>
       <c r="D46" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="71"/>
+      <c r="F46" s="53"/>
     </row>
     <row r="47" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
       <c r="B47" s="29"/>
@@ -2153,130 +2164,130 @@
         <v>4</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E47" s="28"/>
-      <c r="F47" s="71"/>
+      <c r="F47" s="53"/>
     </row>
     <row r="48" spans="2:6" s="4" customFormat="1" ht="15.9" customHeight="1">
       <c r="B48" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" s="33">
         <v>4.01</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="F48" s="71"/>
+        <v>92</v>
+      </c>
+      <c r="F48" s="53"/>
     </row>
     <row r="49" spans="2:9" s="4" customFormat="1" ht="48" customHeight="1">
       <c r="B49" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="7">
         <v>4.0199999999999996</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F49" s="71"/>
+        <v>91</v>
+      </c>
+      <c r="F49" s="53"/>
       <c r="H49" s="3"/>
       <c r="I49"/>
     </row>
-    <row r="50" spans="2:9" s="4" customFormat="1" ht="33.6" customHeight="1" thickBot="1">
+    <row r="50" spans="2:9" s="4" customFormat="1" ht="33.65" customHeight="1" thickBot="1">
       <c r="B50" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" s="7">
         <v>4.03</v>
       </c>
       <c r="D50" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E50" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F50" s="71"/>
-    </row>
-    <row r="51" spans="2:9" s="4" customFormat="1" ht="16.8" customHeight="1" thickTop="1">
+      <c r="F50" s="53"/>
+    </row>
+    <row r="51" spans="2:9" s="4" customFormat="1" ht="16.75" customHeight="1" thickTop="1">
       <c r="B51" s="29"/>
       <c r="C51" s="27">
         <v>5</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E51" s="28"/>
-      <c r="F51" s="71"/>
+      <c r="F51" s="53"/>
     </row>
     <row r="52" spans="2:9" s="4" customFormat="1">
       <c r="B52" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C52" s="33">
         <v>5.01</v>
       </c>
       <c r="D52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="F52" s="71"/>
+        <v>98</v>
+      </c>
+      <c r="F52" s="53"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="2:9" s="4" customFormat="1" ht="31.2">
+    <row r="53" spans="2:9" s="4" customFormat="1" ht="31">
       <c r="B53" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C53" s="7">
         <v>5.0199999999999996</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F53" s="71"/>
+        <v>97</v>
+      </c>
+      <c r="F53" s="53"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="2:9" s="4" customFormat="1" ht="31.2">
+    <row r="54" spans="2:9" s="4" customFormat="1" ht="31">
       <c r="B54" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C54" s="7">
         <v>5.03</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F54" s="71"/>
-    </row>
-    <row r="55" spans="2:9" s="4" customFormat="1" ht="47.4" thickBot="1">
+        <v>83</v>
+      </c>
+      <c r="F54" s="53"/>
+    </row>
+    <row r="55" spans="2:9" s="4" customFormat="1" ht="47" thickBot="1">
       <c r="B55" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C55" s="7">
         <v>5.04</v>
       </c>
       <c r="D55" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F55" s="71"/>
+      <c r="F55" s="53"/>
     </row>
     <row r="56" spans="2:9" s="4" customFormat="1" ht="15.9" customHeight="1" thickTop="1">
       <c r="B56" s="29"/>
@@ -2284,32 +2295,32 @@
         <v>6</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E56" s="28"/>
-      <c r="F56" s="71"/>
-    </row>
-    <row r="57" spans="2:9" ht="140.4">
+      <c r="F56" s="53"/>
+    </row>
+    <row r="57" spans="2:9" ht="139.5">
       <c r="B57" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C57" s="33">
         <v>6.01</v>
       </c>
       <c r="D57" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E57" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F57" s="71"/>
+      <c r="F57" s="53"/>
     </row>
     <row r="58" spans="2:9" ht="15.9" customHeight="1" thickBot="1">
       <c r="B58" s="15"/>
       <c r="C58" s="7"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
-      <c r="F58" s="71"/>
+      <c r="F58" s="53"/>
     </row>
     <row r="59" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
       <c r="B59" s="29"/>
@@ -2317,30 +2328,30 @@
         <v>7</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E59" s="28"/>
-      <c r="F59" s="71"/>
+      <c r="F59" s="53"/>
     </row>
     <row r="60" spans="2:9" ht="15.9" customHeight="1">
       <c r="B60" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60" s="33">
         <v>7.01</v>
       </c>
       <c r="D60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E60" s="24"/>
-      <c r="F60" s="71"/>
+      <c r="F60" s="53"/>
     </row>
     <row r="61" spans="2:9" ht="30" customHeight="1" thickBot="1">
       <c r="B61" s="16"/>
       <c r="C61" s="17"/>
       <c r="D61" s="18"/>
       <c r="E61" s="26"/>
-      <c r="F61" s="71"/>
+      <c r="F61" s="53"/>
     </row>
     <row r="62" spans="2:9" ht="15.9" customHeight="1" thickTop="1">
       <c r="B62" s="29"/>
@@ -2348,70 +2359,70 @@
         <v>8</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E62" s="28"/>
-      <c r="F62" s="71"/>
-    </row>
-    <row r="63" spans="2:9" ht="31.2">
+      <c r="F62" s="53"/>
+    </row>
+    <row r="63" spans="2:9" ht="31">
       <c r="B63" s="41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" s="33">
         <v>8.01</v>
       </c>
       <c r="D63" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F63" s="71"/>
+        <v>107</v>
+      </c>
+      <c r="F63" s="53"/>
     </row>
     <row r="64" spans="2:9">
       <c r="B64" s="40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64" s="7">
         <v>8.02</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="F64" s="71"/>
-    </row>
-    <row r="65" spans="2:6" ht="31.2">
+        <v>105</v>
+      </c>
+      <c r="F64" s="53"/>
+    </row>
+    <row r="65" spans="2:6" ht="31">
       <c r="B65" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" s="7">
         <v>8.0299999999999994</v>
       </c>
       <c r="D65" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="E65" s="72" t="s">
-        <v>109</v>
-      </c>
-      <c r="F65" s="71"/>
-    </row>
-    <row r="66" spans="2:6" ht="31.8" thickBot="1">
-      <c r="B66" s="75" t="s">
-        <v>13</v>
+        <v>79</v>
+      </c>
+      <c r="E65" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="F65" s="53"/>
+    </row>
+    <row r="66" spans="2:6" ht="31.5" thickBot="1">
+      <c r="B66" s="51" t="s">
+        <v>12</v>
       </c>
       <c r="C66" s="43">
         <v>8.0399999999999991</v>
       </c>
-      <c r="D66" s="74" t="s">
-        <v>81</v>
+      <c r="D66" s="50" t="s">
+        <v>80</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F66" s="71"/>
+        <v>106</v>
+      </c>
+      <c r="F66" s="53"/>
     </row>
     <row r="67" spans="2:6" ht="15.9" customHeight="1"/>
     <row r="69" spans="2:6">
@@ -2593,6 +2604,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101000549767899022646ADCD8372B4AFDD77" ma:contentTypeVersion="3" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="52dfa371bc222f35ed99d56e727d4f3c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8c0b0b4-a352-4ab5-8d9a-9b050095665e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f1c2f473d33a4499a8f2166cddfd851" ns2:_="">
     <xsd:import namespace="e8c0b0b4-a352-4ab5-8d9a-9b050095665e"/>
@@ -2730,12 +2747,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB680087-16DE-4BB1-9E43-BA0533F975EB}">
   <ds:schemaRefs>
@@ -2745,6 +2756,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA28E981-D323-4C4F-8BAF-D57797852A0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB33033-905C-4A15-BD49-8FA9F6ECA1E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2760,13 +2780,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA28E981-D323-4C4F-8BAF-D57797852A0D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>